--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -718,11 +718,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lockhyttan, Vstm</t>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104965</v>
+        <v>104968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104968</v>
+        <v>104974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52499-2024 artfynd.xlsx
+++ b/artfynd/A 52499-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137149711</v>
       </c>
       <c r="B2" t="n">
-        <v>104974</v>
+        <v>104976</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
